--- a/data/Math/Multiplier table.xlsx
+++ b/data/Math/Multiplier table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/Math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B1F5ED-D492-554B-A550-880C494C21DE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D011D40-FF16-ED45-8638-69E7A5B023F1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="3600" windowWidth="26660" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t>word</t>
   </si>
@@ -74,47 +74,35 @@
   </si>
   <si>
     <t>sentence</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>chinese</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 X 1 =</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 X 2 =</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 X 3 =</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1 × 4 =</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1 × 5 =</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1 × 6 =</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1 × 7 =</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1 × 8 =</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1 × 9 =</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">2 × 1 =  </t>
@@ -144,58 +132,322 @@
     <t>2 × 9 =</t>
   </si>
   <si>
-    <t xml:space="preserve">3 × 1 =  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 × 2 =  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 × 3 =  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 × 4 =  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 × 5 =  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 × 6 =  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 × 7 =  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 × 8 =  </t>
-  </si>
-  <si>
-    <t>3 × 9 =</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 × 1 =  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 × 2 =  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 × 3 =  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 × 4 =  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 × 5 =  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 × 6 =  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 × 7 =  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 × 8 =  </t>
-  </si>
-  <si>
-    <t>4 × 9 =</t>
+    <t>one one one</t>
+  </si>
+  <si>
+    <t>one two two</t>
+  </si>
+  <si>
+    <t>one three three</t>
+  </si>
+  <si>
+    <t>one four four</t>
+  </si>
+  <si>
+    <t>one five five</t>
+  </si>
+  <si>
+    <t>one six six</t>
+  </si>
+  <si>
+    <t>one seven seven</t>
+  </si>
+  <si>
+    <t>one eight eight</t>
+  </si>
+  <si>
+    <t>one nine nine</t>
+  </si>
+  <si>
+    <t>two one two</t>
+  </si>
+  <si>
+    <t>two two four</t>
+  </si>
+  <si>
+    <t>two three six</t>
+  </si>
+  <si>
+    <t>two four eight</t>
+  </si>
+  <si>
+    <t>two five ten</t>
+  </si>
+  <si>
+    <t>two six twelve</t>
+  </si>
+  <si>
+    <t>two seven fourteen</t>
+  </si>
+  <si>
+    <t>two eight sixteen</t>
+  </si>
+  <si>
+    <t>two nine eighteen</t>
+  </si>
+  <si>
+    <t>1 x 1 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 x 2 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 x 3 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>three one three</t>
+  </si>
+  <si>
+    <t>three two six</t>
+  </si>
+  <si>
+    <t>three three nine</t>
+  </si>
+  <si>
+    <t>three four twelve</t>
+  </si>
+  <si>
+    <t>three five fifteen</t>
+  </si>
+  <si>
+    <t>three six eighteen</t>
+  </si>
+  <si>
+    <t>three seven twenty-one</t>
+  </si>
+  <si>
+    <t>three eight twenty-four</t>
+  </si>
+  <si>
+    <t>three nine twenty-seven</t>
+  </si>
+  <si>
+    <t>four one four</t>
+  </si>
+  <si>
+    <t>four two eight</t>
+  </si>
+  <si>
+    <t>four three twelve</t>
+  </si>
+  <si>
+    <t>four four sixteen</t>
+  </si>
+  <si>
+    <t>four five twenty</t>
+  </si>
+  <si>
+    <t>four six twenty-four</t>
+  </si>
+  <si>
+    <t>four seven twenty-eight</t>
+  </si>
+  <si>
+    <t>four eight thirty-two</t>
+  </si>
+  <si>
+    <t>four nine thirty-six</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 × 1 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">3 × 2 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">3 × 3 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">3 × 4 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">3 × 5 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">3 × 6 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">3 × 7 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">3 × 8 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">3 × 9 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">4 × 1 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">4 × 2 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">4 × 3 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">4 × 4 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">4 × 5 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">4 × 6 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">4 × 7 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">4 × 8 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">4 × 9 = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>five one five</t>
+  </si>
+  <si>
+    <t>five two ten</t>
+  </si>
+  <si>
+    <t>five three fifteen</t>
+  </si>
+  <si>
+    <t>five four twenty</t>
+  </si>
+  <si>
+    <t>five five twenty-five</t>
+  </si>
+  <si>
+    <t>five six thirty</t>
+  </si>
+  <si>
+    <t>five seven thirty-five</t>
+  </si>
+  <si>
+    <t>five eight forty</t>
+  </si>
+  <si>
+    <t>five nine forty-five</t>
+  </si>
+  <si>
+    <t>six one six</t>
+  </si>
+  <si>
+    <t>six two twelve</t>
+  </si>
+  <si>
+    <t>six three eighteen</t>
+  </si>
+  <si>
+    <t>six four twenty-four</t>
+  </si>
+  <si>
+    <t>six five thirty</t>
+  </si>
+  <si>
+    <t>six six thirty-six</t>
+  </si>
+  <si>
+    <t>six seven forty-two</t>
+  </si>
+  <si>
+    <t>six eight forty-eight</t>
+  </si>
+  <si>
+    <t>six nine fifty-four</t>
+  </si>
+  <si>
+    <t>5 × 1 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 × 2 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 × 3 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 × 4 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 × 5 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 × 6 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 × 7 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 × 8 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 × 9 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6 × 1 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6 × 2 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6 × 3 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6 × 4 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6 × 5 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6 × 6 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6 × 7 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6 × 8 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6 × 9 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -213,12 +465,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="20"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -243,6 +489,12 @@
       <sz val="22"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF0F1115"/>
+      <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -304,20 +556,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -602,15 +854,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16" thickBot="1">
+    <row r="1" spans="1:7" ht="16" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -621,404 +873,611 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="30" thickBot="1">
-      <c r="A2" s="6">
-        <v>1</v>
+    <row r="2" spans="1:7" ht="30" thickBot="1">
+      <c r="A2" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="30" thickBot="1">
-      <c r="A3" s="6">
-        <v>2</v>
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" spans="1:7" ht="30" thickBot="1">
+      <c r="A3" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="30" thickBot="1">
-      <c r="A4" s="6">
-        <v>3</v>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" ht="30" thickBot="1">
+      <c r="A4" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="30" thickBot="1">
-      <c r="A5" s="6">
-        <v>4</v>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" spans="1:7" ht="30" thickBot="1">
+      <c r="A5" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="30" thickBot="1">
-      <c r="A6" s="6">
-        <v>5</v>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" ht="30" thickBot="1">
+      <c r="A6" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="30" thickBot="1">
-      <c r="A7" s="6">
-        <v>6</v>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="1:7" ht="30" thickBot="1">
+      <c r="A7" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="1:7" ht="30" thickBot="1">
+      <c r="A8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:7" ht="30" thickBot="1">
+      <c r="A9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="1:7" ht="30" thickBot="1">
+      <c r="A10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="30" thickBot="1">
-      <c r="A8" s="6">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" ht="30" thickBot="1">
+      <c r="A11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="30" thickBot="1">
-      <c r="A9" s="6">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="30" thickBot="1">
-      <c r="A10" s="6">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" thickBot="1">
-      <c r="A11" s="6">
-        <v>2</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="C11" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="30" thickBot="1">
-      <c r="A12" s="6">
+    <row r="12" spans="1:7" ht="30" thickBot="1">
+      <c r="A12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" thickBot="1">
+      <c r="A13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" thickBot="1">
+      <c r="A14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" thickBot="1">
+      <c r="A15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" thickBot="1">
+      <c r="A16" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30" thickBot="1">
+      <c r="A17" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="30" thickBot="1">
+      <c r="A18" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="30" thickBot="1">
+      <c r="A19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="30" thickBot="1">
+      <c r="A20" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="30" thickBot="1">
+      <c r="A21" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="30" thickBot="1">
+      <c r="A22" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="30" thickBot="1">
+      <c r="A23" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="30" thickBot="1">
+      <c r="A24" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="30" thickBot="1">
+      <c r="A25" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="30" thickBot="1">
+      <c r="A26" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30" thickBot="1">
+      <c r="A27" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="30" thickBot="1">
+      <c r="A28" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="30" thickBot="1">
+      <c r="A29" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="2">
         <v>4</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="30" thickBot="1">
-      <c r="A13" s="6">
+    </row>
+    <row r="30" spans="1:3" ht="30" thickBot="1">
+      <c r="A30" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="30" thickBot="1">
+      <c r="A31" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="30" thickBot="1">
+      <c r="A32" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="30" thickBot="1">
+      <c r="A33" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="30" thickBot="1">
+      <c r="A34" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="30" thickBot="1">
+      <c r="A35" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="30" thickBot="1">
+      <c r="A36" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="30" thickBot="1">
+      <c r="A37" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="30" thickBot="1">
+      <c r="A38" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="30" thickBot="1">
+      <c r="A39" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="30" thickBot="1">
+      <c r="A40" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C40" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="30" thickBot="1">
+      <c r="A41" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="30" thickBot="1">
+      <c r="A42" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="30" thickBot="1">
+      <c r="A43" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="30" thickBot="1">
+      <c r="A44" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="30" thickBot="1">
+      <c r="A45" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="30" thickBot="1">
+      <c r="A46" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="30" thickBot="1">
+      <c r="A47" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" s="8">
         <v>6</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="30" thickBot="1">
-      <c r="A14" s="6">
-        <v>8</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="30" thickBot="1">
-      <c r="A15" s="6">
-        <v>10</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="30" thickBot="1">
-      <c r="A16" s="6">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="30" thickBot="1">
-      <c r="A17" s="6">
-        <v>14</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="30" thickBot="1">
-      <c r="A18" s="6">
-        <v>16</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="30" thickBot="1">
-      <c r="A19" s="6">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="30" thickBot="1">
-      <c r="A20" s="6">
-        <v>3</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="30" thickBot="1">
-      <c r="A21" s="6">
+    </row>
+    <row r="48" spans="1:3" ht="30" thickBot="1">
+      <c r="A48" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="8">
         <v>6</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="30" thickBot="1">
-      <c r="A22" s="6">
-        <v>9</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="30" thickBot="1">
-      <c r="A23" s="6">
-        <v>12</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="30" thickBot="1">
-      <c r="A24" s="6">
-        <v>15</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="30" thickBot="1">
-      <c r="A25" s="6">
-        <v>18</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="30" thickBot="1">
-      <c r="A26" s="6">
-        <v>21</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="30" thickBot="1">
-      <c r="A27" s="6">
-        <v>24</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="2">
+    </row>
+    <row r="49" spans="1:3" ht="30" thickBot="1">
+      <c r="A49" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="8">
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="30" thickBot="1">
-      <c r="A28" s="6">
-        <v>27</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="2">
+    <row r="50" spans="1:3" ht="30" thickBot="1">
+      <c r="A50" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C50" s="8">
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="30" thickBot="1">
-      <c r="A29" s="6">
-        <v>4</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="2">
+    <row r="51" spans="1:3" ht="30" thickBot="1">
+      <c r="A51" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" s="8">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="30" thickBot="1">
-      <c r="A30" s="6">
-        <v>8</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="2">
+    <row r="52" spans="1:3" ht="30" thickBot="1">
+      <c r="A52" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="8">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="30" thickBot="1">
-      <c r="A31" s="6">
-        <v>12</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="2">
+    <row r="53" spans="1:3" ht="30" thickBot="1">
+      <c r="A53" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" s="8">
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="30" thickBot="1">
-      <c r="A32" s="6">
-        <v>16</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="30" thickBot="1">
-      <c r="A33" s="6">
-        <v>20</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" s="8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="30" thickBot="1">
-      <c r="A34" s="6">
-        <v>24</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="30" thickBot="1">
-      <c r="A35" s="6">
-        <v>28</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="30" thickBot="1">
-      <c r="A36" s="6">
-        <v>32</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="30" thickBot="1">
-      <c r="A37" s="6">
-        <v>36</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="8">
-        <v>8</v>
+    <row r="54" spans="1:3" ht="30" thickBot="1">
+      <c r="A54" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C54" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="30" thickBot="1">
+      <c r="A55" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C55" s="8">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1089,7 +1548,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Math/Multiplier table.xlsx
+++ b/data/Math/Multiplier table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/Math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D011D40-FF16-ED45-8638-69E7A5B023F1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB88D00-A142-F844-B4D9-B2B254F64508}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="3600" windowWidth="26660" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,18 +132,6 @@
     <t>2 × 9 =</t>
   </si>
   <si>
-    <t>one one one</t>
-  </si>
-  <si>
-    <t>one two two</t>
-  </si>
-  <si>
-    <t>one three three</t>
-  </si>
-  <si>
-    <t>one four four</t>
-  </si>
-  <si>
     <t>one five five</t>
   </si>
   <si>
@@ -447,6 +435,22 @@
   </si>
   <si>
     <t>6 × 9 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>one one (1)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>one two (2)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>one three (3)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>one four (4)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -875,10 +879,10 @@
     </row>
     <row r="2" spans="1:7" ht="30" thickBot="1">
       <c r="A2" s="7" t="s">
-        <v>32</v>
+        <v>121</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -887,10 +891,10 @@
     </row>
     <row r="3" spans="1:7" ht="30" thickBot="1">
       <c r="A3" s="7" t="s">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -899,10 +903,10 @@
     </row>
     <row r="4" spans="1:7" ht="30" thickBot="1">
       <c r="A4" s="7" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
@@ -911,7 +915,7 @@
     </row>
     <row r="5" spans="1:7" ht="30" thickBot="1">
       <c r="A5" s="7" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>17</v>
@@ -923,7 +927,7 @@
     </row>
     <row r="6" spans="1:7" ht="30" thickBot="1">
       <c r="A6" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>18</v>
@@ -935,7 +939,7 @@
     </row>
     <row r="7" spans="1:7" ht="30" thickBot="1">
       <c r="A7" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>19</v>
@@ -947,7 +951,7 @@
     </row>
     <row r="8" spans="1:7" ht="30" thickBot="1">
       <c r="A8" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>20</v>
@@ -959,7 +963,7 @@
     </row>
     <row r="9" spans="1:7" ht="30" thickBot="1">
       <c r="A9" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>21</v>
@@ -971,7 +975,7 @@
     </row>
     <row r="10" spans="1:7" ht="30" thickBot="1">
       <c r="A10" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>22</v>
@@ -983,7 +987,7 @@
     </row>
     <row r="11" spans="1:7" ht="30" thickBot="1">
       <c r="A11" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>23</v>
@@ -994,7 +998,7 @@
     </row>
     <row r="12" spans="1:7" ht="30" thickBot="1">
       <c r="A12" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>24</v>
@@ -1005,7 +1009,7 @@
     </row>
     <row r="13" spans="1:7" ht="30" thickBot="1">
       <c r="A13" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>25</v>
@@ -1016,7 +1020,7 @@
     </row>
     <row r="14" spans="1:7" ht="30" thickBot="1">
       <c r="A14" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>26</v>
@@ -1027,7 +1031,7 @@
     </row>
     <row r="15" spans="1:7" ht="30" thickBot="1">
       <c r="A15" s="7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>27</v>
@@ -1038,7 +1042,7 @@
     </row>
     <row r="16" spans="1:7" ht="30" thickBot="1">
       <c r="A16" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>28</v>
@@ -1049,7 +1053,7 @@
     </row>
     <row r="17" spans="1:3" ht="30" thickBot="1">
       <c r="A17" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>29</v>
@@ -1060,7 +1064,7 @@
     </row>
     <row r="18" spans="1:3" ht="30" thickBot="1">
       <c r="A18" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>30</v>
@@ -1071,7 +1075,7 @@
     </row>
     <row r="19" spans="1:3" ht="30" thickBot="1">
       <c r="A19" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>31</v>
@@ -1082,10 +1086,10 @@
     </row>
     <row r="20" spans="1:3" ht="30" thickBot="1">
       <c r="A20" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
@@ -1093,10 +1097,10 @@
     </row>
     <row r="21" spans="1:3" ht="30" thickBot="1">
       <c r="A21" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
@@ -1104,10 +1108,10 @@
     </row>
     <row r="22" spans="1:3" ht="30" thickBot="1">
       <c r="A22" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -1115,10 +1119,10 @@
     </row>
     <row r="23" spans="1:3" ht="30" thickBot="1">
       <c r="A23" s="7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
@@ -1126,10 +1130,10 @@
     </row>
     <row r="24" spans="1:3" ht="30" thickBot="1">
       <c r="A24" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
@@ -1137,10 +1141,10 @@
     </row>
     <row r="25" spans="1:3" ht="30" thickBot="1">
       <c r="A25" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C25" s="2">
         <v>3</v>
@@ -1148,10 +1152,10 @@
     </row>
     <row r="26" spans="1:3" ht="30" thickBot="1">
       <c r="A26" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C26" s="2">
         <v>3</v>
@@ -1159,10 +1163,10 @@
     </row>
     <row r="27" spans="1:3" ht="30" thickBot="1">
       <c r="A27" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C27" s="2">
         <v>3</v>
@@ -1170,10 +1174,10 @@
     </row>
     <row r="28" spans="1:3" ht="30" thickBot="1">
       <c r="A28" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C28" s="2">
         <v>3</v>
@@ -1181,10 +1185,10 @@
     </row>
     <row r="29" spans="1:3" ht="30" thickBot="1">
       <c r="A29" s="7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C29" s="2">
         <v>4</v>
@@ -1192,10 +1196,10 @@
     </row>
     <row r="30" spans="1:3" ht="30" thickBot="1">
       <c r="A30" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C30" s="2">
         <v>4</v>
@@ -1203,10 +1207,10 @@
     </row>
     <row r="31" spans="1:3" ht="30" thickBot="1">
       <c r="A31" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C31" s="2">
         <v>4</v>
@@ -1214,10 +1218,10 @@
     </row>
     <row r="32" spans="1:3" ht="30" thickBot="1">
       <c r="A32" s="7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C32" s="2">
         <v>4</v>
@@ -1225,10 +1229,10 @@
     </row>
     <row r="33" spans="1:3" ht="30" thickBot="1">
       <c r="A33" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C33" s="2">
         <v>4</v>
@@ -1236,10 +1240,10 @@
     </row>
     <row r="34" spans="1:3" ht="30" thickBot="1">
       <c r="A34" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C34" s="2">
         <v>4</v>
@@ -1247,10 +1251,10 @@
     </row>
     <row r="35" spans="1:3" ht="30" thickBot="1">
       <c r="A35" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C35" s="2">
         <v>4</v>
@@ -1258,10 +1262,10 @@
     </row>
     <row r="36" spans="1:3" ht="30" thickBot="1">
       <c r="A36" s="7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C36" s="2">
         <v>4</v>
@@ -1269,10 +1273,10 @@
     </row>
     <row r="37" spans="1:3" ht="30" thickBot="1">
       <c r="A37" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C37" s="2">
         <v>4</v>
@@ -1280,10 +1284,10 @@
     </row>
     <row r="38" spans="1:3" ht="30" thickBot="1">
       <c r="A38" s="7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C38" s="8">
         <v>5</v>
@@ -1291,10 +1295,10 @@
     </row>
     <row r="39" spans="1:3" ht="30" thickBot="1">
       <c r="A39" s="7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C39" s="8">
         <v>5</v>
@@ -1302,10 +1306,10 @@
     </row>
     <row r="40" spans="1:3" ht="30" thickBot="1">
       <c r="A40" s="7" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C40" s="8">
         <v>5</v>
@@ -1313,10 +1317,10 @@
     </row>
     <row r="41" spans="1:3" ht="30" thickBot="1">
       <c r="A41" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C41" s="8">
         <v>5</v>
@@ -1324,10 +1328,10 @@
     </row>
     <row r="42" spans="1:3" ht="30" thickBot="1">
       <c r="A42" s="7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C42" s="8">
         <v>5</v>
@@ -1335,10 +1339,10 @@
     </row>
     <row r="43" spans="1:3" ht="30" thickBot="1">
       <c r="A43" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C43" s="8">
         <v>5</v>
@@ -1346,10 +1350,10 @@
     </row>
     <row r="44" spans="1:3" ht="30" thickBot="1">
       <c r="A44" s="7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C44" s="8">
         <v>5</v>
@@ -1357,10 +1361,10 @@
     </row>
     <row r="45" spans="1:3" ht="30" thickBot="1">
       <c r="A45" s="7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C45" s="8">
         <v>5</v>
@@ -1368,10 +1372,10 @@
     </row>
     <row r="46" spans="1:3" ht="30" thickBot="1">
       <c r="A46" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C46" s="8">
         <v>5</v>
@@ -1379,10 +1383,10 @@
     </row>
     <row r="47" spans="1:3" ht="30" thickBot="1">
       <c r="A47" s="7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C47" s="8">
         <v>6</v>
@@ -1390,10 +1394,10 @@
     </row>
     <row r="48" spans="1:3" ht="30" thickBot="1">
       <c r="A48" s="7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C48" s="8">
         <v>6</v>
@@ -1401,10 +1405,10 @@
     </row>
     <row r="49" spans="1:3" ht="30" thickBot="1">
       <c r="A49" s="7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C49" s="8">
         <v>6</v>
@@ -1412,10 +1416,10 @@
     </row>
     <row r="50" spans="1:3" ht="30" thickBot="1">
       <c r="A50" s="7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C50" s="8">
         <v>6</v>
@@ -1423,10 +1427,10 @@
     </row>
     <row r="51" spans="1:3" ht="30" thickBot="1">
       <c r="A51" s="7" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C51" s="8">
         <v>6</v>
@@ -1434,10 +1438,10 @@
     </row>
     <row r="52" spans="1:3" ht="30" thickBot="1">
       <c r="A52" s="7" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C52" s="8">
         <v>6</v>
@@ -1445,10 +1449,10 @@
     </row>
     <row r="53" spans="1:3" ht="30" thickBot="1">
       <c r="A53" s="7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C53" s="8">
         <v>6</v>
@@ -1456,10 +1460,10 @@
     </row>
     <row r="54" spans="1:3" ht="30" thickBot="1">
       <c r="A54" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C54" s="8">
         <v>6</v>
@@ -1467,10 +1471,10 @@
     </row>
     <row r="55" spans="1:3" ht="30" thickBot="1">
       <c r="A55" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C55" s="8">
         <v>6</v>

--- a/data/Math/Multiplier table.xlsx
+++ b/data/Math/Multiplier table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/Math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB88D00-A142-F844-B4D9-B2B254F64508}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EB3156-8CBA-9E4E-918A-91A6D483A8AE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="3600" windowWidth="26660" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/Math/Multiplier table.xlsx
+++ b/data/Math/Multiplier table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/Math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EB3156-8CBA-9E4E-918A-91A6D483A8AE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0731BE3-F5EB-E146-A497-4BC4443AF96D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="3600" windowWidth="26660" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,19 +438,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>one one (1)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>one two (2)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>one three (3)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>one four (4)</t>
+    <t>one one 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>one two 2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>one three 3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>one four 4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/data/Math/Multiplier table.xlsx
+++ b/data/Math/Multiplier table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/Math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0731BE3-F5EB-E146-A497-4BC4443AF96D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCDEBA03-BBFF-F943-8B67-0DE14FB44BC1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="3600" windowWidth="26660" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/Math/Multiplier table.xlsx
+++ b/data/Math/Multiplier table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/Math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCDEBA03-BBFF-F943-8B67-0DE14FB44BC1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E06BE08-2AC7-D949-AF2A-74540B5F6A0C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="3600" windowWidth="26660" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t>word</t>
   </si>
@@ -132,48 +132,6 @@
     <t>2 × 9 =</t>
   </si>
   <si>
-    <t>one five five</t>
-  </si>
-  <si>
-    <t>one six six</t>
-  </si>
-  <si>
-    <t>one seven seven</t>
-  </si>
-  <si>
-    <t>one eight eight</t>
-  </si>
-  <si>
-    <t>one nine nine</t>
-  </si>
-  <si>
-    <t>two one two</t>
-  </si>
-  <si>
-    <t>two two four</t>
-  </si>
-  <si>
-    <t>two three six</t>
-  </si>
-  <si>
-    <t>two four eight</t>
-  </si>
-  <si>
-    <t>two five ten</t>
-  </si>
-  <si>
-    <t>two six twelve</t>
-  </si>
-  <si>
-    <t>two seven fourteen</t>
-  </si>
-  <si>
-    <t>two eight sixteen</t>
-  </si>
-  <si>
-    <t>two nine eighteen</t>
-  </si>
-  <si>
     <t>1 x 1 =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -186,60 +144,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>three one three</t>
-  </si>
-  <si>
-    <t>three two six</t>
-  </si>
-  <si>
-    <t>three three nine</t>
-  </si>
-  <si>
-    <t>three four twelve</t>
-  </si>
-  <si>
-    <t>three five fifteen</t>
-  </si>
-  <si>
-    <t>three six eighteen</t>
-  </si>
-  <si>
-    <t>three seven twenty-one</t>
-  </si>
-  <si>
-    <t>three eight twenty-four</t>
-  </si>
-  <si>
-    <t>three nine twenty-seven</t>
-  </si>
-  <si>
-    <t>four one four</t>
-  </si>
-  <si>
-    <t>four two eight</t>
-  </si>
-  <si>
-    <t>four three twelve</t>
-  </si>
-  <si>
-    <t>four four sixteen</t>
-  </si>
-  <si>
-    <t>four five twenty</t>
-  </si>
-  <si>
-    <t>four six twenty-four</t>
-  </si>
-  <si>
-    <t>four seven twenty-eight</t>
-  </si>
-  <si>
-    <t>four eight thirty-two</t>
-  </si>
-  <si>
-    <t>four nine thirty-six</t>
-  </si>
-  <si>
     <t xml:space="preserve">3 × 1 = </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -312,60 +216,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>five one five</t>
-  </si>
-  <si>
-    <t>five two ten</t>
-  </si>
-  <si>
-    <t>five three fifteen</t>
-  </si>
-  <si>
-    <t>five four twenty</t>
-  </si>
-  <si>
-    <t>five five twenty-five</t>
-  </si>
-  <si>
-    <t>five six thirty</t>
-  </si>
-  <si>
-    <t>five seven thirty-five</t>
-  </si>
-  <si>
-    <t>five eight forty</t>
-  </si>
-  <si>
-    <t>five nine forty-five</t>
-  </si>
-  <si>
-    <t>six one six</t>
-  </si>
-  <si>
-    <t>six two twelve</t>
-  </si>
-  <si>
-    <t>six three eighteen</t>
-  </si>
-  <si>
-    <t>six four twenty-four</t>
-  </si>
-  <si>
-    <t>six five thirty</t>
-  </si>
-  <si>
-    <t>six six thirty-six</t>
-  </si>
-  <si>
-    <t>six seven forty-two</t>
-  </si>
-  <si>
-    <t>six eight forty-eight</t>
-  </si>
-  <si>
-    <t>six nine fifty-four</t>
-  </si>
-  <si>
     <t>5 × 1 =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -439,18 +289,353 @@
   </si>
   <si>
     <t>one one 1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>one two 2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>one three 3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>one four 4</t>
+  </si>
+  <si>
+    <t>one five 5</t>
+  </si>
+  <si>
+    <t>one six 6</t>
+  </si>
+  <si>
+    <t>one seven 7</t>
+  </si>
+  <si>
+    <t>one eight 8</t>
+  </si>
+  <si>
+    <t>one nine 9</t>
+  </si>
+  <si>
+    <t>two one 2</t>
+  </si>
+  <si>
+    <t>two two 4</t>
+  </si>
+  <si>
+    <t>two three 6</t>
+  </si>
+  <si>
+    <t>two four 8</t>
+  </si>
+  <si>
+    <t>two five 10</t>
+  </si>
+  <si>
+    <t>two six 12</t>
+  </si>
+  <si>
+    <t>two seven 14</t>
+  </si>
+  <si>
+    <t>two eight 16</t>
+  </si>
+  <si>
+    <t>two nine 18</t>
+  </si>
+  <si>
+    <t>three one 3</t>
+  </si>
+  <si>
+    <t>three two 6</t>
+  </si>
+  <si>
+    <t>three three 9</t>
+  </si>
+  <si>
+    <t>three four 12</t>
+  </si>
+  <si>
+    <t>three five 15</t>
+  </si>
+  <si>
+    <t>three six 18</t>
+  </si>
+  <si>
+    <t>three seven 21</t>
+  </si>
+  <si>
+    <t>three eight 24</t>
+  </si>
+  <si>
+    <t>three nine 27</t>
+  </si>
+  <si>
+    <t>four one 4</t>
+  </si>
+  <si>
+    <t>four two 8</t>
+  </si>
+  <si>
+    <t>four three 12</t>
+  </si>
+  <si>
+    <t>four four 16</t>
+  </si>
+  <si>
+    <t>four five 20</t>
+  </si>
+  <si>
+    <t>four six 24</t>
+  </si>
+  <si>
+    <t>four seven 28</t>
+  </si>
+  <si>
+    <t>four eight 32</t>
+  </si>
+  <si>
+    <t>four nine 36</t>
+  </si>
+  <si>
+    <t>five one 5</t>
+  </si>
+  <si>
+    <t>five two 10</t>
+  </si>
+  <si>
+    <t>five three 15</t>
+  </si>
+  <si>
+    <t>five four 20</t>
+  </si>
+  <si>
+    <t>five five 25</t>
+  </si>
+  <si>
+    <t>five six 30</t>
+  </si>
+  <si>
+    <t>five seven 35</t>
+  </si>
+  <si>
+    <t>five eight 40</t>
+  </si>
+  <si>
+    <t>five nine 45</t>
+  </si>
+  <si>
+    <t>six one 6</t>
+  </si>
+  <si>
+    <t>six two 12</t>
+  </si>
+  <si>
+    <t>six three 18</t>
+  </si>
+  <si>
+    <t>six four 24</t>
+  </si>
+  <si>
+    <t>six five 30</t>
+  </si>
+  <si>
+    <t>six six 36</t>
+  </si>
+  <si>
+    <t>six seven 42</t>
+  </si>
+  <si>
+    <t>six eight 48</t>
+  </si>
+  <si>
+    <t>six nine 54</t>
+  </si>
+  <si>
+    <t>seven one 7</t>
+  </si>
+  <si>
+    <t>seven two 14</t>
+  </si>
+  <si>
+    <t>seven three 21</t>
+  </si>
+  <si>
+    <t>seven four 28</t>
+  </si>
+  <si>
+    <t>seven five 35</t>
+  </si>
+  <si>
+    <t>seven six 42</t>
+  </si>
+  <si>
+    <t>seven seven 49</t>
+  </si>
+  <si>
+    <t>seven eight 56</t>
+  </si>
+  <si>
+    <t>seven nine 63</t>
+  </si>
+  <si>
+    <t>eight one 8</t>
+  </si>
+  <si>
+    <t>eight two 16</t>
+  </si>
+  <si>
+    <t>eight three 24</t>
+  </si>
+  <si>
+    <t>eight four 32</t>
+  </si>
+  <si>
+    <t>eight five 40</t>
+  </si>
+  <si>
+    <t>eight six 48</t>
+  </si>
+  <si>
+    <t>eight seven 56</t>
+  </si>
+  <si>
+    <t>eight eight 64</t>
+  </si>
+  <si>
+    <t>eight nine 72</t>
+  </si>
+  <si>
+    <t>nine one 9</t>
+  </si>
+  <si>
+    <t>nine two 18</t>
+  </si>
+  <si>
+    <t>nine three 27</t>
+  </si>
+  <si>
+    <t>nine four 36</t>
+  </si>
+  <si>
+    <t>nine five 45</t>
+  </si>
+  <si>
+    <t>nine six 54</t>
+  </si>
+  <si>
+    <t>nine seven 63</t>
+  </si>
+  <si>
+    <t>nine eight 72</t>
+  </si>
+  <si>
+    <t>nine nine 81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 × 1 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">7 × 2 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">7 × 3 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">7 × 4 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">7 × 5 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">7 × 6 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">7 × 7 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">7 × 8 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7 × 9 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">8 × 1 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">8 × 2 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">8 × 3 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">8 × 4 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">8 × 5 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">8 × 6 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">8 × 7 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">8 × 8 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8 × 9 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">9 × 1 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">9 × 2 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">9 × 3 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">9 × 4 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">9 × 5 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">9 × 6 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">9 × 7 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">9 × 8 =  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9 × 9 =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -858,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -879,10 +1064,10 @@
     </row>
     <row r="2" spans="1:7" ht="30" thickBot="1">
       <c r="A2" s="7" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -891,10 +1076,10 @@
     </row>
     <row r="3" spans="1:7" ht="30" thickBot="1">
       <c r="A3" s="7" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -903,10 +1088,10 @@
     </row>
     <row r="4" spans="1:7" ht="30" thickBot="1">
       <c r="A4" s="7" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
@@ -915,7 +1100,7 @@
     </row>
     <row r="5" spans="1:7" ht="30" thickBot="1">
       <c r="A5" s="7" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>17</v>
@@ -927,7 +1112,7 @@
     </row>
     <row r="6" spans="1:7" ht="30" thickBot="1">
       <c r="A6" s="7" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>18</v>
@@ -939,7 +1124,7 @@
     </row>
     <row r="7" spans="1:7" ht="30" thickBot="1">
       <c r="A7" s="7" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>19</v>
@@ -951,7 +1136,7 @@
     </row>
     <row r="8" spans="1:7" ht="30" thickBot="1">
       <c r="A8" s="7" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>20</v>
@@ -963,7 +1148,7 @@
     </row>
     <row r="9" spans="1:7" ht="30" thickBot="1">
       <c r="A9" s="7" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>21</v>
@@ -975,7 +1160,7 @@
     </row>
     <row r="10" spans="1:7" ht="30" thickBot="1">
       <c r="A10" s="7" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>22</v>
@@ -987,7 +1172,7 @@
     </row>
     <row r="11" spans="1:7" ht="30" thickBot="1">
       <c r="A11" s="7" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>23</v>
@@ -998,7 +1183,7 @@
     </row>
     <row r="12" spans="1:7" ht="30" thickBot="1">
       <c r="A12" s="7" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>24</v>
@@ -1009,7 +1194,7 @@
     </row>
     <row r="13" spans="1:7" ht="30" thickBot="1">
       <c r="A13" s="7" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>25</v>
@@ -1020,7 +1205,7 @@
     </row>
     <row r="14" spans="1:7" ht="30" thickBot="1">
       <c r="A14" s="7" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>26</v>
@@ -1031,7 +1216,7 @@
     </row>
     <row r="15" spans="1:7" ht="30" thickBot="1">
       <c r="A15" s="7" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>27</v>
@@ -1042,7 +1227,7 @@
     </row>
     <row r="16" spans="1:7" ht="30" thickBot="1">
       <c r="A16" s="7" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>28</v>
@@ -1053,7 +1238,7 @@
     </row>
     <row r="17" spans="1:3" ht="30" thickBot="1">
       <c r="A17" s="7" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>29</v>
@@ -1064,7 +1249,7 @@
     </row>
     <row r="18" spans="1:3" ht="30" thickBot="1">
       <c r="A18" s="7" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>30</v>
@@ -1075,7 +1260,7 @@
     </row>
     <row r="19" spans="1:3" ht="30" thickBot="1">
       <c r="A19" s="7" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>31</v>
@@ -1086,10 +1271,10 @@
     </row>
     <row r="20" spans="1:3" ht="30" thickBot="1">
       <c r="A20" s="7" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
@@ -1097,10 +1282,10 @@
     </row>
     <row r="21" spans="1:3" ht="30" thickBot="1">
       <c r="A21" s="7" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
@@ -1108,10 +1293,10 @@
     </row>
     <row r="22" spans="1:3" ht="30" thickBot="1">
       <c r="A22" s="7" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -1119,10 +1304,10 @@
     </row>
     <row r="23" spans="1:3" ht="30" thickBot="1">
       <c r="A23" s="7" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
@@ -1130,10 +1315,10 @@
     </row>
     <row r="24" spans="1:3" ht="30" thickBot="1">
       <c r="A24" s="7" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
@@ -1141,10 +1326,10 @@
     </row>
     <row r="25" spans="1:3" ht="30" thickBot="1">
       <c r="A25" s="7" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="C25" s="2">
         <v>3</v>
@@ -1152,10 +1337,10 @@
     </row>
     <row r="26" spans="1:3" ht="30" thickBot="1">
       <c r="A26" s="7" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="C26" s="2">
         <v>3</v>
@@ -1163,10 +1348,10 @@
     </row>
     <row r="27" spans="1:3" ht="30" thickBot="1">
       <c r="A27" s="7" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="C27" s="2">
         <v>3</v>
@@ -1174,10 +1359,10 @@
     </row>
     <row r="28" spans="1:3" ht="30" thickBot="1">
       <c r="A28" s="7" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C28" s="2">
         <v>3</v>
@@ -1185,10 +1370,10 @@
     </row>
     <row r="29" spans="1:3" ht="30" thickBot="1">
       <c r="A29" s="7" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="C29" s="2">
         <v>4</v>
@@ -1196,10 +1381,10 @@
     </row>
     <row r="30" spans="1:3" ht="30" thickBot="1">
       <c r="A30" s="7" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="C30" s="2">
         <v>4</v>
@@ -1207,10 +1392,10 @@
     </row>
     <row r="31" spans="1:3" ht="30" thickBot="1">
       <c r="A31" s="7" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C31" s="2">
         <v>4</v>
@@ -1218,10 +1403,10 @@
     </row>
     <row r="32" spans="1:3" ht="30" thickBot="1">
       <c r="A32" s="7" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="C32" s="2">
         <v>4</v>
@@ -1229,10 +1414,10 @@
     </row>
     <row r="33" spans="1:3" ht="30" thickBot="1">
       <c r="A33" s="7" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="C33" s="2">
         <v>4</v>
@@ -1240,10 +1425,10 @@
     </row>
     <row r="34" spans="1:3" ht="30" thickBot="1">
       <c r="A34" s="7" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="C34" s="2">
         <v>4</v>
@@ -1251,10 +1436,10 @@
     </row>
     <row r="35" spans="1:3" ht="30" thickBot="1">
       <c r="A35" s="7" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="C35" s="2">
         <v>4</v>
@@ -1262,10 +1447,10 @@
     </row>
     <row r="36" spans="1:3" ht="30" thickBot="1">
       <c r="A36" s="7" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="C36" s="2">
         <v>4</v>
@@ -1273,10 +1458,10 @@
     </row>
     <row r="37" spans="1:3" ht="30" thickBot="1">
       <c r="A37" s="7" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="C37" s="2">
         <v>4</v>
@@ -1284,10 +1469,10 @@
     </row>
     <row r="38" spans="1:3" ht="30" thickBot="1">
       <c r="A38" s="7" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="C38" s="8">
         <v>5</v>
@@ -1295,10 +1480,10 @@
     </row>
     <row r="39" spans="1:3" ht="30" thickBot="1">
       <c r="A39" s="7" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="C39" s="8">
         <v>5</v>
@@ -1306,10 +1491,10 @@
     </row>
     <row r="40" spans="1:3" ht="30" thickBot="1">
       <c r="A40" s="7" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="C40" s="8">
         <v>5</v>
@@ -1317,10 +1502,10 @@
     </row>
     <row r="41" spans="1:3" ht="30" thickBot="1">
       <c r="A41" s="7" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="C41" s="8">
         <v>5</v>
@@ -1328,10 +1513,10 @@
     </row>
     <row r="42" spans="1:3" ht="30" thickBot="1">
       <c r="A42" s="7" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="C42" s="8">
         <v>5</v>
@@ -1339,10 +1524,10 @@
     </row>
     <row r="43" spans="1:3" ht="30" thickBot="1">
       <c r="A43" s="7" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="C43" s="8">
         <v>5</v>
@@ -1350,10 +1535,10 @@
     </row>
     <row r="44" spans="1:3" ht="30" thickBot="1">
       <c r="A44" s="7" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="C44" s="8">
         <v>5</v>
@@ -1361,10 +1546,10 @@
     </row>
     <row r="45" spans="1:3" ht="30" thickBot="1">
       <c r="A45" s="7" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="C45" s="8">
         <v>5</v>
@@ -1372,10 +1557,10 @@
     </row>
     <row r="46" spans="1:3" ht="30" thickBot="1">
       <c r="A46" s="7" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="C46" s="8">
         <v>5</v>
@@ -1383,10 +1568,10 @@
     </row>
     <row r="47" spans="1:3" ht="30" thickBot="1">
       <c r="A47" s="7" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="C47" s="8">
         <v>6</v>
@@ -1394,10 +1579,10 @@
     </row>
     <row r="48" spans="1:3" ht="30" thickBot="1">
       <c r="A48" s="7" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="C48" s="8">
         <v>6</v>
@@ -1405,10 +1590,10 @@
     </row>
     <row r="49" spans="1:3" ht="30" thickBot="1">
       <c r="A49" s="7" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="C49" s="8">
         <v>6</v>
@@ -1416,10 +1601,10 @@
     </row>
     <row r="50" spans="1:3" ht="30" thickBot="1">
       <c r="A50" s="7" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="C50" s="8">
         <v>6</v>
@@ -1427,10 +1612,10 @@
     </row>
     <row r="51" spans="1:3" ht="30" thickBot="1">
       <c r="A51" s="7" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="C51" s="8">
         <v>6</v>
@@ -1438,10 +1623,10 @@
     </row>
     <row r="52" spans="1:3" ht="30" thickBot="1">
       <c r="A52" s="7" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="C52" s="8">
         <v>6</v>
@@ -1449,10 +1634,10 @@
     </row>
     <row r="53" spans="1:3" ht="30" thickBot="1">
       <c r="A53" s="7" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="C53" s="8">
         <v>6</v>
@@ -1460,10 +1645,10 @@
     </row>
     <row r="54" spans="1:3" ht="30" thickBot="1">
       <c r="A54" s="7" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="C54" s="8">
         <v>6</v>
@@ -1471,13 +1656,310 @@
     </row>
     <row r="55" spans="1:3" ht="30" thickBot="1">
       <c r="A55" s="7" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="C55" s="8">
         <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="30" thickBot="1">
+      <c r="A56" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C56" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="30" thickBot="1">
+      <c r="A57" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C57" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="30" thickBot="1">
+      <c r="A58" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C58" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="30" thickBot="1">
+      <c r="A59" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C59" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="30" thickBot="1">
+      <c r="A60" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C60" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="30" thickBot="1">
+      <c r="A61" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C61" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="30" thickBot="1">
+      <c r="A62" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C62" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="30" thickBot="1">
+      <c r="A63" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C63" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="30" thickBot="1">
+      <c r="A64" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C64" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="30" thickBot="1">
+      <c r="A65" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C65" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="30" thickBot="1">
+      <c r="A66" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C66" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="30" thickBot="1">
+      <c r="A67" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C67" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="30" thickBot="1">
+      <c r="A68" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C68" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="30" thickBot="1">
+      <c r="A69" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C69" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="30" thickBot="1">
+      <c r="A70" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C70" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="30" thickBot="1">
+      <c r="A71" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C71" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="30" thickBot="1">
+      <c r="A72" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C72" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="30" thickBot="1">
+      <c r="A73" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C73" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="30" thickBot="1">
+      <c r="A74" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C74" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="30" thickBot="1">
+      <c r="A75" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C75" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="30" thickBot="1">
+      <c r="A76" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C76" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="30" thickBot="1">
+      <c r="A77" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C77" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="30" thickBot="1">
+      <c r="A78" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C78" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="30" thickBot="1">
+      <c r="A79" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C79" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="30" thickBot="1">
+      <c r="A80" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="30" thickBot="1">
+      <c r="A81" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C81" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="30" thickBot="1">
+      <c r="A82" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C82" s="8">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/Math/Multiplier table.xlsx
+++ b/data/Math/Multiplier table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/Math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E06BE08-2AC7-D949-AF2A-74540B5F6A0C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC46117F-F6D3-B74F-90E9-4C8CD50BDBAF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="3600" windowWidth="26660" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="169">
   <si>
     <t>word</t>
   </si>
@@ -37,42 +37,6 @@
     <t>day</t>
   </si>
   <si>
-    <t>We follow rules every day.</t>
-  </si>
-  <si>
-    <t>我們每天都遵守規則。</t>
-  </si>
-  <si>
-    <t>There are rules for things we do at home, at school, and in a lot of other places.</t>
-  </si>
-  <si>
-    <t>我們在家裡、學校和許多其他地方做事都有規則。</t>
-  </si>
-  <si>
-    <t>We should always be polite and take turns when we play games.</t>
-  </si>
-  <si>
-    <t>我們玩遊戲時應該要有禮貌，並且輪流進行。</t>
-  </si>
-  <si>
-    <t>The crossing guards help us cross the road safely, and we should pay attention to the traffic light.</t>
-  </si>
-  <si>
-    <t>交通導護人員幫助我們安全過馬路，我們應該注意紅綠燈。</t>
-  </si>
-  <si>
-    <t>We must listen to the lifeguards because they help us stay safe in and near the water.</t>
-  </si>
-  <si>
-    <t>我們必須聽從救生員的話，因為他們幫助我們在水裡和水邊保持安全。</t>
-  </si>
-  <si>
-    <t>Rules tell us what we should and shouldn't do, and they help keep us safe, happy and healthy.</t>
-  </si>
-  <si>
-    <t>規則告訴我們應該做什麼、不應該做什麼，並幫助我們保持安全、快樂和健康。</t>
-  </si>
-  <si>
     <t>sentence</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -636,6 +600,14 @@
   </si>
   <si>
     <t>9 × 9 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>No sentences</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>沒有句子</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1064,10 +1036,10 @@
     </row>
     <row r="2" spans="1:7" ht="30" thickBot="1">
       <c r="A2" s="7" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -1076,10 +1048,10 @@
     </row>
     <row r="3" spans="1:7" ht="30" thickBot="1">
       <c r="A3" s="7" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -1088,10 +1060,10 @@
     </row>
     <row r="4" spans="1:7" ht="30" thickBot="1">
       <c r="A4" s="7" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
@@ -1100,10 +1072,10 @@
     </row>
     <row r="5" spans="1:7" ht="30" thickBot="1">
       <c r="A5" s="7" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -1112,10 +1084,10 @@
     </row>
     <row r="6" spans="1:7" ht="30" thickBot="1">
       <c r="A6" s="7" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -1124,10 +1096,10 @@
     </row>
     <row r="7" spans="1:7" ht="30" thickBot="1">
       <c r="A7" s="7" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -1136,10 +1108,10 @@
     </row>
     <row r="8" spans="1:7" ht="30" thickBot="1">
       <c r="A8" s="7" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
@@ -1148,10 +1120,10 @@
     </row>
     <row r="9" spans="1:7" ht="30" thickBot="1">
       <c r="A9" s="7" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -1160,10 +1132,10 @@
     </row>
     <row r="10" spans="1:7" ht="30" thickBot="1">
       <c r="A10" s="7" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2">
         <v>1</v>
@@ -1172,10 +1144,10 @@
     </row>
     <row r="11" spans="1:7" ht="30" thickBot="1">
       <c r="A11" s="7" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2">
         <v>2</v>
@@ -1183,10 +1155,10 @@
     </row>
     <row r="12" spans="1:7" ht="30" thickBot="1">
       <c r="A12" s="7" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
@@ -1194,10 +1166,10 @@
     </row>
     <row r="13" spans="1:7" ht="30" thickBot="1">
       <c r="A13" s="7" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C13" s="2">
         <v>2</v>
@@ -1205,10 +1177,10 @@
     </row>
     <row r="14" spans="1:7" ht="30" thickBot="1">
       <c r="A14" s="7" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C14" s="2">
         <v>2</v>
@@ -1216,10 +1188,10 @@
     </row>
     <row r="15" spans="1:7" ht="30" thickBot="1">
       <c r="A15" s="7" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C15" s="2">
         <v>2</v>
@@ -1227,10 +1199,10 @@
     </row>
     <row r="16" spans="1:7" ht="30" thickBot="1">
       <c r="A16" s="7" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
@@ -1238,10 +1210,10 @@
     </row>
     <row r="17" spans="1:3" ht="30" thickBot="1">
       <c r="A17" s="7" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2">
         <v>2</v>
@@ -1249,10 +1221,10 @@
     </row>
     <row r="18" spans="1:3" ht="30" thickBot="1">
       <c r="A18" s="7" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2">
         <v>2</v>
@@ -1260,10 +1232,10 @@
     </row>
     <row r="19" spans="1:3" ht="30" thickBot="1">
       <c r="A19" s="7" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C19" s="2">
         <v>2</v>
@@ -1271,10 +1243,10 @@
     </row>
     <row r="20" spans="1:3" ht="30" thickBot="1">
       <c r="A20" s="7" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
@@ -1282,10 +1254,10 @@
     </row>
     <row r="21" spans="1:3" ht="30" thickBot="1">
       <c r="A21" s="7" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
@@ -1293,10 +1265,10 @@
     </row>
     <row r="22" spans="1:3" ht="30" thickBot="1">
       <c r="A22" s="7" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -1304,10 +1276,10 @@
     </row>
     <row r="23" spans="1:3" ht="30" thickBot="1">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
@@ -1315,10 +1287,10 @@
     </row>
     <row r="24" spans="1:3" ht="30" thickBot="1">
       <c r="A24" s="7" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
@@ -1326,10 +1298,10 @@
     </row>
     <row r="25" spans="1:3" ht="30" thickBot="1">
       <c r="A25" s="7" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C25" s="2">
         <v>3</v>
@@ -1337,10 +1309,10 @@
     </row>
     <row r="26" spans="1:3" ht="30" thickBot="1">
       <c r="A26" s="7" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C26" s="2">
         <v>3</v>
@@ -1348,10 +1320,10 @@
     </row>
     <row r="27" spans="1:3" ht="30" thickBot="1">
       <c r="A27" s="7" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C27" s="2">
         <v>3</v>
@@ -1359,10 +1331,10 @@
     </row>
     <row r="28" spans="1:3" ht="30" thickBot="1">
       <c r="A28" s="7" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C28" s="2">
         <v>3</v>
@@ -1370,10 +1342,10 @@
     </row>
     <row r="29" spans="1:3" ht="30" thickBot="1">
       <c r="A29" s="7" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C29" s="2">
         <v>4</v>
@@ -1381,10 +1353,10 @@
     </row>
     <row r="30" spans="1:3" ht="30" thickBot="1">
       <c r="A30" s="7" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C30" s="2">
         <v>4</v>
@@ -1392,10 +1364,10 @@
     </row>
     <row r="31" spans="1:3" ht="30" thickBot="1">
       <c r="A31" s="7" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C31" s="2">
         <v>4</v>
@@ -1403,10 +1375,10 @@
     </row>
     <row r="32" spans="1:3" ht="30" thickBot="1">
       <c r="A32" s="7" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C32" s="2">
         <v>4</v>
@@ -1414,10 +1386,10 @@
     </row>
     <row r="33" spans="1:3" ht="30" thickBot="1">
       <c r="A33" s="7" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C33" s="2">
         <v>4</v>
@@ -1425,10 +1397,10 @@
     </row>
     <row r="34" spans="1:3" ht="30" thickBot="1">
       <c r="A34" s="7" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C34" s="2">
         <v>4</v>
@@ -1436,10 +1408,10 @@
     </row>
     <row r="35" spans="1:3" ht="30" thickBot="1">
       <c r="A35" s="7" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C35" s="2">
         <v>4</v>
@@ -1447,10 +1419,10 @@
     </row>
     <row r="36" spans="1:3" ht="30" thickBot="1">
       <c r="A36" s="7" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C36" s="2">
         <v>4</v>
@@ -1458,10 +1430,10 @@
     </row>
     <row r="37" spans="1:3" ht="30" thickBot="1">
       <c r="A37" s="7" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C37" s="2">
         <v>4</v>
@@ -1469,10 +1441,10 @@
     </row>
     <row r="38" spans="1:3" ht="30" thickBot="1">
       <c r="A38" s="7" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C38" s="8">
         <v>5</v>
@@ -1480,10 +1452,10 @@
     </row>
     <row r="39" spans="1:3" ht="30" thickBot="1">
       <c r="A39" s="7" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C39" s="8">
         <v>5</v>
@@ -1491,10 +1463,10 @@
     </row>
     <row r="40" spans="1:3" ht="30" thickBot="1">
       <c r="A40" s="7" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C40" s="8">
         <v>5</v>
@@ -1502,10 +1474,10 @@
     </row>
     <row r="41" spans="1:3" ht="30" thickBot="1">
       <c r="A41" s="7" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C41" s="8">
         <v>5</v>
@@ -1513,10 +1485,10 @@
     </row>
     <row r="42" spans="1:3" ht="30" thickBot="1">
       <c r="A42" s="7" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C42" s="8">
         <v>5</v>
@@ -1524,10 +1496,10 @@
     </row>
     <row r="43" spans="1:3" ht="30" thickBot="1">
       <c r="A43" s="7" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C43" s="8">
         <v>5</v>
@@ -1535,10 +1507,10 @@
     </row>
     <row r="44" spans="1:3" ht="30" thickBot="1">
       <c r="A44" s="7" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C44" s="8">
         <v>5</v>
@@ -1546,10 +1518,10 @@
     </row>
     <row r="45" spans="1:3" ht="30" thickBot="1">
       <c r="A45" s="7" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C45" s="8">
         <v>5</v>
@@ -1557,10 +1529,10 @@
     </row>
     <row r="46" spans="1:3" ht="30" thickBot="1">
       <c r="A46" s="7" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C46" s="8">
         <v>5</v>
@@ -1568,10 +1540,10 @@
     </row>
     <row r="47" spans="1:3" ht="30" thickBot="1">
       <c r="A47" s="7" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C47" s="8">
         <v>6</v>
@@ -1579,10 +1551,10 @@
     </row>
     <row r="48" spans="1:3" ht="30" thickBot="1">
       <c r="A48" s="7" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C48" s="8">
         <v>6</v>
@@ -1590,10 +1562,10 @@
     </row>
     <row r="49" spans="1:3" ht="30" thickBot="1">
       <c r="A49" s="7" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C49" s="8">
         <v>6</v>
@@ -1601,10 +1573,10 @@
     </row>
     <row r="50" spans="1:3" ht="30" thickBot="1">
       <c r="A50" s="7" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C50" s="8">
         <v>6</v>
@@ -1612,10 +1584,10 @@
     </row>
     <row r="51" spans="1:3" ht="30" thickBot="1">
       <c r="A51" s="7" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C51" s="8">
         <v>6</v>
@@ -1623,10 +1595,10 @@
     </row>
     <row r="52" spans="1:3" ht="30" thickBot="1">
       <c r="A52" s="7" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C52" s="8">
         <v>6</v>
@@ -1634,10 +1606,10 @@
     </row>
     <row r="53" spans="1:3" ht="30" thickBot="1">
       <c r="A53" s="7" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C53" s="8">
         <v>6</v>
@@ -1645,10 +1617,10 @@
     </row>
     <row r="54" spans="1:3" ht="30" thickBot="1">
       <c r="A54" s="7" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C54" s="8">
         <v>6</v>
@@ -1656,10 +1628,10 @@
     </row>
     <row r="55" spans="1:3" ht="30" thickBot="1">
       <c r="A55" s="7" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C55" s="8">
         <v>6</v>
@@ -1667,10 +1639,10 @@
     </row>
     <row r="56" spans="1:3" ht="30" thickBot="1">
       <c r="A56" s="7" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C56" s="8">
         <v>7</v>
@@ -1678,10 +1650,10 @@
     </row>
     <row r="57" spans="1:3" ht="30" thickBot="1">
       <c r="A57" s="7" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C57" s="8">
         <v>7</v>
@@ -1689,10 +1661,10 @@
     </row>
     <row r="58" spans="1:3" ht="30" thickBot="1">
       <c r="A58" s="7" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C58" s="8">
         <v>7</v>
@@ -1700,10 +1672,10 @@
     </row>
     <row r="59" spans="1:3" ht="30" thickBot="1">
       <c r="A59" s="7" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C59" s="8">
         <v>7</v>
@@ -1711,10 +1683,10 @@
     </row>
     <row r="60" spans="1:3" ht="30" thickBot="1">
       <c r="A60" s="7" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C60" s="8">
         <v>7</v>
@@ -1722,10 +1694,10 @@
     </row>
     <row r="61" spans="1:3" ht="30" thickBot="1">
       <c r="A61" s="7" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C61" s="8">
         <v>7</v>
@@ -1733,10 +1705,10 @@
     </row>
     <row r="62" spans="1:3" ht="30" thickBot="1">
       <c r="A62" s="7" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C62" s="8">
         <v>7</v>
@@ -1744,10 +1716,10 @@
     </row>
     <row r="63" spans="1:3" ht="30" thickBot="1">
       <c r="A63" s="7" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="C63" s="8">
         <v>7</v>
@@ -1755,10 +1727,10 @@
     </row>
     <row r="64" spans="1:3" ht="30" thickBot="1">
       <c r="A64" s="7" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C64" s="8">
         <v>7</v>
@@ -1766,10 +1738,10 @@
     </row>
     <row r="65" spans="1:3" ht="30" thickBot="1">
       <c r="A65" s="7" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="C65" s="8">
         <v>8</v>
@@ -1777,10 +1749,10 @@
     </row>
     <row r="66" spans="1:3" ht="30" thickBot="1">
       <c r="A66" s="7" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="C66" s="8">
         <v>8</v>
@@ -1788,10 +1760,10 @@
     </row>
     <row r="67" spans="1:3" ht="30" thickBot="1">
       <c r="A67" s="7" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C67" s="8">
         <v>8</v>
@@ -1799,10 +1771,10 @@
     </row>
     <row r="68" spans="1:3" ht="30" thickBot="1">
       <c r="A68" s="7" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C68" s="8">
         <v>8</v>
@@ -1810,10 +1782,10 @@
     </row>
     <row r="69" spans="1:3" ht="30" thickBot="1">
       <c r="A69" s="7" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C69" s="8">
         <v>8</v>
@@ -1821,10 +1793,10 @@
     </row>
     <row r="70" spans="1:3" ht="30" thickBot="1">
       <c r="A70" s="7" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C70" s="8">
         <v>8</v>
@@ -1832,10 +1804,10 @@
     </row>
     <row r="71" spans="1:3" ht="30" thickBot="1">
       <c r="A71" s="7" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="C71" s="8">
         <v>8</v>
@@ -1843,10 +1815,10 @@
     </row>
     <row r="72" spans="1:3" ht="30" thickBot="1">
       <c r="A72" s="7" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C72" s="8">
         <v>8</v>
@@ -1854,10 +1826,10 @@
     </row>
     <row r="73" spans="1:3" ht="30" thickBot="1">
       <c r="A73" s="7" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C73" s="8">
         <v>8</v>
@@ -1865,10 +1837,10 @@
     </row>
     <row r="74" spans="1:3" ht="30" thickBot="1">
       <c r="A74" s="7" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C74" s="8">
         <v>9</v>
@@ -1876,10 +1848,10 @@
     </row>
     <row r="75" spans="1:3" ht="30" thickBot="1">
       <c r="A75" s="7" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C75" s="8">
         <v>9</v>
@@ -1887,10 +1859,10 @@
     </row>
     <row r="76" spans="1:3" ht="30" thickBot="1">
       <c r="A76" s="7" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C76" s="8">
         <v>9</v>
@@ -1898,10 +1870,10 @@
     </row>
     <row r="77" spans="1:3" ht="30" thickBot="1">
       <c r="A77" s="7" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C77" s="8">
         <v>9</v>
@@ -1909,10 +1881,10 @@
     </row>
     <row r="78" spans="1:3" ht="30" thickBot="1">
       <c r="A78" s="7" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C78" s="8">
         <v>9</v>
@@ -1920,10 +1892,10 @@
     </row>
     <row r="79" spans="1:3" ht="30" thickBot="1">
       <c r="A79" s="7" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C79" s="8">
         <v>9</v>
@@ -1931,10 +1903,10 @@
     </row>
     <row r="80" spans="1:3" ht="30" thickBot="1">
       <c r="A80" s="7" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C80" s="8">
         <v>9</v>
@@ -1942,10 +1914,10 @@
     </row>
     <row r="81" spans="1:3" ht="30" thickBot="1">
       <c r="A81" s="7" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="C81" s="8">
         <v>9</v>
@@ -1953,10 +1925,10 @@
     </row>
     <row r="82" spans="1:3" ht="30" thickBot="1">
       <c r="A82" s="7" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="C82" s="8">
         <v>9</v>
@@ -1971,7 +1943,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DCD9B3D-005E-BC4C-AB7B-106DE368F76B}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="84.33203125" bestFit="1" customWidth="1"/>
@@ -1979,58 +1951,18 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>167</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
